--- a/tabelas/2022.xlsx
+++ b/tabelas/2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Acadêmico Juliano Zanoni\Engenharia de Software\Projetos Engenharia\Projetos\narrativapilotodois-portfolio\tabelas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA4D509C-1D01-442D-8830-A7F067E27CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27B91DD7-B19F-4D08-ACA4-251CA152711C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{349979B7-C21B-407A-A293-DC1F6033EF36}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="201">
   <si>
     <t>INSCRICAO</t>
   </si>
@@ -677,7 +677,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -687,7 +687,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1002,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FEC8DEA-D1AE-4B91-B66D-48CA0A2026FB}">
-  <dimension ref="A1:K118"/>
+  <dimension ref="A1:K122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1085,7 +1084,7 @@
       <c r="A3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -4833,40 +4832,23 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F118" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G118" s="2">
-        <v>2022</v>
-      </c>
-      <c r="H118" s="2">
-        <v>0</v>
-      </c>
-      <c r="I118" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J118" t="s">
-        <v>29</v>
-      </c>
-      <c r="K118" t="s">
-        <v>31</v>
-      </c>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" s="4"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" s="4"/>
+      <c r="J120" s="2"/>
+      <c r="K120" s="2"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" s="4"/>
+      <c r="J121" s="2"/>
+      <c r="K121" s="2"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" s="4"/>
+      <c r="J122" s="2"/>
+      <c r="K122" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
